--- a/outputs/reports/catboost_v2/feature_importance_top10.xlsx
+++ b/outputs/reports/catboost_v2/feature_importance_top10.xlsx
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.07850951358445041</v>
+        <v>0.08023667168105225</v>
       </c>
       <c r="F2" t="n">
-        <v>7.850951358445034</v>
+        <v>8.023667168105233</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=7.85%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=8.02%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -506,19 +506,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.05953418487611781</v>
+        <v>0.05965870228360584</v>
       </c>
       <c r="F3" t="n">
-        <v>5.953418487611776</v>
+        <v>5.965870228360589</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.95%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.97%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -542,19 +542,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.05902799501884216</v>
+        <v>0.05335637252486698</v>
       </c>
       <c r="F4" t="n">
-        <v>5.902799501884211</v>
+        <v>5.335637252486702</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=5.90%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.34%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05060763118691404</v>
+        <v>0.05006322781991538</v>
       </c>
       <c r="F5" t="n">
-        <v>5.060763118691399</v>
+        <v>5.006322781991543</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=5.01%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.04418441392537081</v>
+        <v>0.0477082008322463</v>
       </c>
       <c r="F6" t="n">
-        <v>4.418441392537077</v>
+        <v>4.770820083224634</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.42%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.77%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04395703343026858</v>
+        <v>0.04639196940201325</v>
       </c>
       <c r="F7" t="n">
-        <v>4.395703343026854</v>
+        <v>4.639196940201328</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.40%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.64%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04225371024686373</v>
+        <v>0.04564792997314992</v>
       </c>
       <c r="F8" t="n">
-        <v>4.225371024686369</v>
+        <v>4.564792997314996</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.23%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.56%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03613249857830451</v>
+        <v>0.03961817449756503</v>
       </c>
       <c r="F9" t="n">
-        <v>3.613249857830448</v>
+        <v>3.961817449756506</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.61%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.96%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03327229716580977</v>
+        <v>0.03674398613046026</v>
       </c>
       <c r="F10" t="n">
-        <v>3.327229716580975</v>
+        <v>3.674398613046029</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.33%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.67%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.03315060255846319</v>
+        <v>0.03496440685152415</v>
       </c>
       <c r="F11" t="n">
-        <v>3.315060255846316</v>
+        <v>3.496440685152419</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=3.32%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.50%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>

--- a/outputs/reports/catboost_v2/feature_importance_top10.xlsx
+++ b/outputs/reports/catboost_v2/feature_importance_top10.xlsx
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.08023667168105225</v>
+        <v>0.07427712080084094</v>
       </c>
       <c r="F2" t="n">
-        <v>8.023667168105233</v>
+        <v>7.427712080084095</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=8.02%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=7.43%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -506,19 +506,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.05965870228360584</v>
+        <v>0.06172011341010498</v>
       </c>
       <c r="F3" t="n">
-        <v>5.965870228360589</v>
+        <v>6.172011341010498</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.97%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.17%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.05335637252486698</v>
+        <v>0.05379237014250506</v>
       </c>
       <c r="F4" t="n">
-        <v>5.335637252486702</v>
+        <v>5.379237014250506</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.34%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.38%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05006322781991538</v>
+        <v>0.04966963952217231</v>
       </c>
       <c r="F5" t="n">
-        <v>5.006322781991543</v>
+        <v>4.966963952217232</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=5.01%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.97%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0477082008322463</v>
+        <v>0.04847747741277377</v>
       </c>
       <c r="F6" t="n">
-        <v>4.770820083224634</v>
+        <v>4.847747741277378</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.77%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=4.85%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04639196940201325</v>
+        <v>0.04379704642749314</v>
       </c>
       <c r="F7" t="n">
-        <v>4.639196940201328</v>
+        <v>4.379704642749314</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.64%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.38%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>FLD_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>분야코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04564792997314992</v>
+        <v>0.04286335922902603</v>
       </c>
       <c r="F8" t="n">
-        <v>4.564792997314996</v>
+        <v>4.286335922902603</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.56%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 분야코드(FLD_CD). 기여도(정규화 비중)=4.29%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03961817449756503</v>
+        <v>0.0357887121699075</v>
       </c>
       <c r="F9" t="n">
-        <v>3.961817449756506</v>
+        <v>3.57887121699075</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.96%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.58%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03674398613046026</v>
+        <v>0.03530508698139623</v>
       </c>
       <c r="F10" t="n">
-        <v>3.674398613046029</v>
+        <v>3.530508698139623</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.67%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=3.53%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.03496440685152415</v>
+        <v>0.03030561248217348</v>
       </c>
       <c r="F11" t="n">
-        <v>3.496440685152419</v>
+        <v>3.030561248217349</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.50%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=3.03%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
